--- a/Outputs/Proyecciones.xlsx
+++ b/Outputs/Proyecciones.xlsx
@@ -109,9 +109,6 @@
     <t xml:space="preserve">M2_err</t>
   </si>
   <si>
-    <t xml:space="preserve">dic 2025</t>
-  </si>
-  <si>
     <t xml:space="preserve">ene 2026</t>
   </si>
   <si>
@@ -127,6 +124,9 @@
     <t xml:space="preserve">may 2026</t>
   </si>
   <si>
+    <t xml:space="preserve">jun 2026</t>
+  </si>
+  <si>
     <t xml:space="preserve">Modelo</t>
   </si>
   <si>
@@ -175,141 +175,141 @@
     <t xml:space="preserve">ARIMA(1,1,1)</t>
   </si>
   <si>
+    <t xml:space="preserve">ARIMA(2,0,3)</t>
+  </si>
+  <si>
     <t xml:space="preserve">ARIMA(2,1,2)</t>
   </si>
   <si>
     <t xml:space="preserve">ARIMA(0,1,2)</t>
   </si>
   <si>
+    <t xml:space="preserve">ARIMA(4,1,1)</t>
+  </si>
+  <si>
     <t xml:space="preserve">ARIMA(4,1,4)</t>
   </si>
   <si>
-    <t xml:space="preserve">ARIMA(4,1,1)</t>
-  </si>
-  <si>
     <t xml:space="preserve">ARIMA(4,1,2)</t>
   </si>
   <si>
+    <t xml:space="preserve">ARIMA(1,1,4)</t>
+  </si>
+  <si>
     <t xml:space="preserve">ARIMA(0,1,3)</t>
   </si>
   <si>
+    <t xml:space="preserve">ARIMA(1,1,2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARIMA(2,1,1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARIMA(2,1,3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARIMA(3,0,3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARIMA(3,1,2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARIMA(3,1,3)</t>
+  </si>
+  <si>
     <t xml:space="preserve">ARIMA(0,1,1)</t>
   </si>
   <si>
-    <t xml:space="preserve">ARIMA(1,1,2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARIMA(2,1,1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARIMA(3,0,3)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARIMA(3,1,3)</t>
-  </si>
-  <si>
     <t xml:space="preserve">ARIMA(0,1,4)</t>
   </si>
   <si>
     <t xml:space="preserve">ARIMA(3,0,4)</t>
   </si>
   <si>
-    <t xml:space="preserve">ARIMA(2,1,3)</t>
-  </si>
-  <si>
     <t xml:space="preserve">ARIMA(1,0,0)</t>
   </si>
   <si>
+    <t xml:space="preserve">ARIMA(2,0,1)</t>
+  </si>
+  <si>
     <t xml:space="preserve">ARIMA(1,1,3)</t>
   </si>
   <si>
-    <t xml:space="preserve">ARIMA(2,0,1)</t>
-  </si>
-  <si>
     <t xml:space="preserve">ARIMA(4,1,3)</t>
   </si>
   <si>
+    <t xml:space="preserve">ARIMA(1,1,0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARIMA(3,1,1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARIMA(4,0,4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARIMA(4,1,0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARIMA(2,0,0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARIMA(1,0,1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARIMA(0,0,2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARIMA(3,0,1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARIMA(2,0,2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARIMA(1,0,4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARIMA(0,0,3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARIMA(1,0,2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARIMA(0,0,1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARIMA(3,0,2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARIMA(4,0,2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARIMA(3,0,0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARIMA(0,1,0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARIMA(0,0,4)</t>
+  </si>
+  <si>
     <t xml:space="preserve">ARIMA(3,1,0)</t>
   </si>
   <si>
-    <t xml:space="preserve">ARIMA(1,1,0)</t>
-  </si>
-  <si>
     <t xml:space="preserve">ARIMA(2,1,0)</t>
   </si>
   <si>
-    <t xml:space="preserve">ARIMA(3,1,1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARIMA(4,1,0)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARIMA(1,1,4)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARIMA(4,0,4)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARIMA(2,0,2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARIMA(3,0,1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARIMA(2,0,0)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARIMA(1,0,1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARIMA(0,0,2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARIMA(3,1,2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARIMA(0,0,3)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARIMA(1,0,2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARIMA(3,0,2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARIMA(2,0,3)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARIMA(3,0,0)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARIMA(0,0,1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARIMA(4,0,2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARIMA(0,1,0)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARIMA(1,0,4)</t>
+    <t xml:space="preserve">ARIMA(2,0,4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARIMA(4,0,3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARIMA(1,0,3)</t>
   </si>
   <si>
     <t xml:space="preserve">ARIMA(4,0,0)</t>
   </si>
   <si>
-    <t xml:space="preserve">ARIMA(0,0,4)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARIMA(2,0,4)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARIMA(1,0,3)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARIMA(4,0,3)</t>
-  </si>
-  <si>
     <t xml:space="preserve">ARIMA(4,0,1)</t>
   </si>
   <si>
@@ -328,64 +328,64 @@
     <t xml:space="preserve">Modelo ganador</t>
   </si>
   <si>
-    <t xml:space="preserve">-3.966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-1.623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-254.88</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.56</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-251.82</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-253.98</t>
+    <t xml:space="preserve">-3.61</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.67</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-261.96</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-258.85</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.64</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-261.03</t>
   </si>
   <si>
     <t xml:space="preserve">RMSE (train)</t>
   </si>
   <si>
-    <t xml:space="preserve">0.756849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.009308</t>
+    <t xml:space="preserve">0.766707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.009239</t>
   </si>
   <si>
     <t xml:space="preserve">MAPE (train)</t>
   </si>
   <si>
-    <t xml:space="preserve">132.9199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.1222</t>
+    <t xml:space="preserve">135.6402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.122</t>
   </si>
   <si>
     <t xml:space="preserve">RMSE backtest (IPC)</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6779</t>
+    <t xml:space="preserve">5.6192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3555</t>
   </si>
   <si>
     <t xml:space="preserve">MAPE backtest (IPC)</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.82%</t>
+    <t xml:space="preserve">3.45%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14%</t>
   </si>
 </sst>
 </file>
@@ -1813,21 +1813,23 @@
       <c r="B43" t="s">
         <v>14</v>
       </c>
-      <c r="C43"/>
+      <c r="C43" t="n">
+        <v>154.22</v>
+      </c>
       <c r="D43" t="n">
-        <v>154.7836</v>
+        <v>154.22</v>
       </c>
       <c r="E43" t="n">
-        <v>153.2532</v>
+        <v>154.22</v>
       </c>
       <c r="F43" t="n">
-        <v>9.63</v>
+        <v>9.23</v>
       </c>
       <c r="G43" t="n">
-        <v>8.55</v>
+        <v>9.23</v>
       </c>
       <c r="H43" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="44">
@@ -1839,16 +1841,16 @@
       </c>
       <c r="C44"/>
       <c r="D44" t="n">
-        <v>156.8676</v>
+        <v>155.8301</v>
       </c>
       <c r="E44" t="n">
-        <v>154.8798</v>
+        <v>156.6115</v>
       </c>
       <c r="F44" t="n">
-        <v>9.79</v>
+        <v>9.06</v>
       </c>
       <c r="G44" t="n">
-        <v>8.4</v>
+        <v>9.61</v>
       </c>
       <c r="H44" t="s">
         <v>21</v>
@@ -1863,16 +1865,16 @@
       </c>
       <c r="C45"/>
       <c r="D45" t="n">
-        <v>158.4309</v>
+        <v>157.199</v>
       </c>
       <c r="E45" t="n">
-        <v>156.0413</v>
+        <v>158.3701</v>
       </c>
       <c r="F45" t="n">
-        <v>9.78</v>
+        <v>8.93</v>
       </c>
       <c r="G45" t="n">
-        <v>8.12</v>
+        <v>9.74</v>
       </c>
       <c r="H45" t="s">
         <v>21</v>
@@ -1887,16 +1889,16 @@
       </c>
       <c r="C46"/>
       <c r="D46" t="n">
-        <v>160.2231</v>
+        <v>158.848</v>
       </c>
       <c r="E46" t="n">
-        <v>156.8687</v>
+        <v>159.6587</v>
       </c>
       <c r="F46" t="n">
-        <v>10.8</v>
+        <v>9.85</v>
       </c>
       <c r="G46" t="n">
-        <v>8.48</v>
+        <v>10.41</v>
       </c>
       <c r="H46" t="s">
         <v>21</v>
@@ -1911,16 +1913,16 @@
       </c>
       <c r="C47"/>
       <c r="D47" t="n">
-        <v>162.1564</v>
+        <v>160.6814</v>
       </c>
       <c r="E47" t="n">
-        <v>157.4569</v>
+        <v>160.6002</v>
       </c>
       <c r="F47" t="n">
-        <v>11.3</v>
+        <v>10.28</v>
       </c>
       <c r="G47" t="n">
-        <v>8.07</v>
+        <v>10.23</v>
       </c>
       <c r="H47" t="s">
         <v>21</v>
@@ -1935,16 +1937,16 @@
       </c>
       <c r="C48"/>
       <c r="D48" t="n">
-        <v>163.7778</v>
+        <v>162.093</v>
       </c>
       <c r="E48" t="n">
-        <v>157.8745</v>
+        <v>161.287</v>
       </c>
       <c r="F48" t="n">
-        <v>11.97</v>
+        <v>10.81</v>
       </c>
       <c r="G48" t="n">
-        <v>7.93</v>
+        <v>10.26</v>
       </c>
       <c r="H48" t="s">
         <v>21</v>
@@ -1959,18 +1961,42 @@
       </c>
       <c r="C49"/>
       <c r="D49" t="n">
-        <v>165.7952</v>
+        <v>164.0159</v>
       </c>
       <c r="E49" t="n">
-        <v>158.1707</v>
+        <v>161.7872</v>
       </c>
       <c r="F49" t="n">
-        <v>12.68</v>
+        <v>11.47</v>
       </c>
       <c r="G49" t="n">
-        <v>7.5</v>
+        <v>9.96</v>
       </c>
       <c r="H49" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B50" t="s">
+        <v>8</v>
+      </c>
+      <c r="C50"/>
+      <c r="D50" t="n">
+        <v>165.5929</v>
+      </c>
+      <c r="E50" t="n">
+        <v>162.1511</v>
+      </c>
+      <c r="F50" t="n">
+        <v>11.09</v>
+      </c>
+      <c r="G50" t="n">
+        <v>8.78</v>
+      </c>
+      <c r="H50" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2016,25 +2042,25 @@
         <v>2026</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="n">
-        <v>154.7836</v>
+        <v>155.8301</v>
       </c>
       <c r="D2" t="n">
-        <v>153.2532</v>
+        <v>156.6115</v>
       </c>
       <c r="E2" t="n">
-        <v>9.63</v>
+        <v>9.06</v>
       </c>
       <c r="F2" t="n">
-        <v>8.55</v>
+        <v>9.61</v>
       </c>
       <c r="G2" t="n">
-        <v>150.41</v>
+        <v>153.73</v>
       </c>
       <c r="H2" t="n">
-        <v>156.15</v>
+        <v>159.54</v>
       </c>
     </row>
     <row r="3">
@@ -2042,25 +2068,25 @@
         <v>2026</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" t="n">
-        <v>156.8676</v>
+        <v>157.199</v>
       </c>
       <c r="D3" t="n">
-        <v>154.8798</v>
+        <v>158.3701</v>
       </c>
       <c r="E3" t="n">
-        <v>9.79</v>
+        <v>8.93</v>
       </c>
       <c r="F3" t="n">
-        <v>8.4</v>
+        <v>9.74</v>
       </c>
       <c r="G3" t="n">
-        <v>149.25</v>
+        <v>152.62</v>
       </c>
       <c r="H3" t="n">
-        <v>160.72</v>
+        <v>164.34</v>
       </c>
     </row>
     <row r="4">
@@ -2068,25 +2094,25 @@
         <v>2026</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" t="n">
-        <v>158.4309</v>
+        <v>158.848</v>
       </c>
       <c r="D4" t="n">
-        <v>156.0413</v>
+        <v>159.6587</v>
       </c>
       <c r="E4" t="n">
-        <v>9.78</v>
+        <v>9.85</v>
       </c>
       <c r="F4" t="n">
-        <v>8.12</v>
+        <v>10.41</v>
       </c>
       <c r="G4" t="n">
-        <v>147.62</v>
+        <v>150.99</v>
       </c>
       <c r="H4" t="n">
-        <v>164.94</v>
+        <v>168.82</v>
       </c>
     </row>
     <row r="5">
@@ -2094,25 +2120,25 @@
         <v>2026</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5" t="n">
-        <v>160.2231</v>
+        <v>160.6814</v>
       </c>
       <c r="D5" t="n">
-        <v>156.8687</v>
+        <v>160.6002</v>
       </c>
       <c r="E5" t="n">
-        <v>10.8</v>
+        <v>10.28</v>
       </c>
       <c r="F5" t="n">
-        <v>8.48</v>
+        <v>10.23</v>
       </c>
       <c r="G5" t="n">
-        <v>145.78</v>
+        <v>149.12</v>
       </c>
       <c r="H5" t="n">
-        <v>168.8</v>
+        <v>172.97</v>
       </c>
     </row>
     <row r="6">
@@ -2120,25 +2146,25 @@
         <v>2026</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6" t="n">
-        <v>162.1564</v>
+        <v>162.093</v>
       </c>
       <c r="D6" t="n">
-        <v>157.4569</v>
+        <v>161.287</v>
       </c>
       <c r="E6" t="n">
-        <v>11.3</v>
+        <v>10.81</v>
       </c>
       <c r="F6" t="n">
-        <v>8.07</v>
+        <v>10.26</v>
       </c>
       <c r="G6" t="n">
-        <v>143.87</v>
+        <v>147.14</v>
       </c>
       <c r="H6" t="n">
-        <v>172.33</v>
+        <v>176.79</v>
       </c>
     </row>
     <row r="7">
@@ -2146,51 +2172,51 @@
         <v>2026</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" t="n">
-        <v>163.7778</v>
+        <v>164.0159</v>
       </c>
       <c r="D7" t="n">
-        <v>157.8745</v>
+        <v>161.7872</v>
       </c>
       <c r="E7" t="n">
-        <v>11.97</v>
+        <v>11.47</v>
       </c>
       <c r="F7" t="n">
-        <v>7.93</v>
+        <v>9.96</v>
       </c>
       <c r="G7" t="n">
-        <v>141.97</v>
+        <v>145.16</v>
       </c>
       <c r="H7" t="n">
-        <v>175.56</v>
+        <v>180.32</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="C8" t="n">
-        <v>165.7952</v>
+        <v>165.5929</v>
       </c>
       <c r="D8" t="n">
-        <v>158.1707</v>
+        <v>162.1511</v>
       </c>
       <c r="E8" t="n">
-        <v>12.68</v>
+        <v>11.09</v>
       </c>
       <c r="F8" t="n">
-        <v>7.5</v>
+        <v>8.78</v>
       </c>
       <c r="G8" t="n">
-        <v>140.12</v>
+        <v>143.22</v>
       </c>
       <c r="H8" t="n">
-        <v>178.54</v>
+        <v>183.59</v>
       </c>
     </row>
   </sheetData>
@@ -2229,19 +2255,19 @@
         <v>30</v>
       </c>
       <c r="B2" t="n">
-        <v>147.14</v>
+        <v>149.06</v>
       </c>
       <c r="C2" t="n">
-        <v>146.46</v>
+        <v>150.3</v>
       </c>
       <c r="D2" t="n">
-        <v>146.7</v>
+        <v>147.77</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.68</v>
+        <v>1.24</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.44</v>
+        <v>-1.29</v>
       </c>
     </row>
     <row r="3">
@@ -2249,19 +2275,19 @@
         <v>31</v>
       </c>
       <c r="B3" t="n">
-        <v>149.06</v>
+        <v>148.14</v>
       </c>
       <c r="C3" t="n">
-        <v>149.1</v>
+        <v>151.52</v>
       </c>
       <c r="D3" t="n">
-        <v>147</v>
+        <v>148.23</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04</v>
+        <v>3.38</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.06</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="4">
@@ -2269,19 +2295,19 @@
         <v>32</v>
       </c>
       <c r="B4" t="n">
-        <v>148.14</v>
+        <v>147.63</v>
       </c>
       <c r="C4" t="n">
-        <v>149.97</v>
+        <v>153.8</v>
       </c>
       <c r="D4" t="n">
-        <v>147.23</v>
+        <v>148.57</v>
       </c>
       <c r="E4" t="n">
-        <v>1.83</v>
+        <v>6.17</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.91</v>
+        <v>0.94</v>
       </c>
     </row>
     <row r="5">
@@ -2289,19 +2315,19 @@
         <v>33</v>
       </c>
       <c r="B5" t="n">
-        <v>147.63</v>
+        <v>147.84</v>
       </c>
       <c r="C5" t="n">
-        <v>152.06</v>
+        <v>155.84</v>
       </c>
       <c r="D5" t="n">
-        <v>147.39</v>
+        <v>148.82</v>
       </c>
       <c r="E5" t="n">
-        <v>4.42</v>
+        <v>8</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.24</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="6">
@@ -2309,19 +2335,19 @@
         <v>34</v>
       </c>
       <c r="B6" t="n">
-        <v>147.84</v>
+        <v>150.98</v>
       </c>
       <c r="C6" t="n">
-        <v>153.92</v>
+        <v>157.41</v>
       </c>
       <c r="D6" t="n">
-        <v>147.51</v>
+        <v>149</v>
       </c>
       <c r="E6" t="n">
-        <v>6.08</v>
+        <v>6.43</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.32</v>
+        <v>-1.98</v>
       </c>
     </row>
     <row r="7">
@@ -2329,19 +2355,19 @@
         <v>35</v>
       </c>
       <c r="B7" t="n">
-        <v>150.98</v>
+        <v>154.22</v>
       </c>
       <c r="C7" t="n">
-        <v>155.13</v>
+        <v>159.97</v>
       </c>
       <c r="D7" t="n">
-        <v>147.6</v>
+        <v>149.14</v>
       </c>
       <c r="E7" t="n">
-        <v>4.14</v>
+        <v>5.75</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.39</v>
+        <v>-5.08</v>
       </c>
     </row>
   </sheetData>
@@ -2407,25 +2433,25 @@
         <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>115.2359</v>
+        <v>116.6679</v>
       </c>
       <c r="F2" t="n">
-        <v>123.558</v>
+        <v>125.269</v>
       </c>
       <c r="G2" t="n">
-        <v>116.0104</v>
+        <v>117.6419</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7568</v>
+        <v>0.7667</v>
       </c>
       <c r="I2" t="n">
-        <v>132.9199</v>
+        <v>135.6402</v>
       </c>
       <c r="J2" t="n">
-        <v>0.5346</v>
+        <v>0.6001</v>
       </c>
       <c r="K2" t="n">
-        <v>-3.966</v>
+        <v>-3.61</v>
       </c>
       <c r="L2" t="s">
         <v>49</v>
@@ -2445,25 +2471,25 @@
         <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>118.3356</v>
+        <v>119.6172</v>
       </c>
       <c r="F3" t="n">
-        <v>127.2014</v>
+        <v>128.8257</v>
       </c>
       <c r="G3" t="n">
-        <v>118.5756</v>
+        <v>120.1091</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7577</v>
+        <v>0.7499</v>
       </c>
       <c r="I3" t="n">
-        <v>130.0451</v>
+        <v>125.9283</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3977</v>
+        <v>0.4533</v>
       </c>
       <c r="K3" t="n">
-        <v>-2.8813</v>
+        <v>-2.8231</v>
       </c>
       <c r="L3" t="s">
         <v>49</v>
@@ -2483,25 +2509,25 @@
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>114.6555</v>
+        <v>116.6881</v>
       </c>
       <c r="F4" t="n">
-        <v>119.0555</v>
+        <v>121.1802</v>
       </c>
       <c r="G4" t="n">
-        <v>115.8207</v>
+        <v>117.9115</v>
       </c>
       <c r="H4" t="n">
-        <v>0.912</v>
+        <v>0.905</v>
       </c>
       <c r="I4" t="n">
-        <v>166.5292</v>
+        <v>157.9807</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2276</v>
+        <v>0.1416</v>
       </c>
       <c r="K4" t="n">
-        <v>-2.2652</v>
+        <v>-2.1491</v>
       </c>
       <c r="L4" t="s">
         <v>49</v>
@@ -2515,31 +2541,31 @@
         <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>116.7267</v>
+        <v>116.8787</v>
       </c>
       <c r="F5" t="n">
-        <v>123.4064</v>
+        <v>125.7483</v>
       </c>
       <c r="G5" t="n">
-        <v>118.0152</v>
+        <v>118.0431</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8601</v>
+        <v>0.753</v>
       </c>
       <c r="I5" t="n">
-        <v>156.1664</v>
+        <v>428.2072</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1775</v>
+        <v>0.596</v>
       </c>
       <c r="K5" t="n">
-        <v>-2.0417</v>
+        <v>-2.0243</v>
       </c>
       <c r="L5" t="s">
         <v>49</v>
@@ -2550,7 +2576,7 @@
         <v>53</v>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
         <v>1</v>
@@ -2559,25 +2585,25 @@
         <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>114.7241</v>
+        <v>118.5464</v>
       </c>
       <c r="F6" t="n">
-        <v>119.124</v>
+        <v>125.4</v>
       </c>
       <c r="G6" t="n">
-        <v>115.8893</v>
+        <v>119.952</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9151</v>
+        <v>0.8523</v>
       </c>
       <c r="I6" t="n">
-        <v>218.7788</v>
+        <v>147.3792</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1992</v>
+        <v>0.1201</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.8557</v>
+        <v>-1.9278</v>
       </c>
       <c r="L6" t="s">
         <v>49</v>
@@ -2588,34 +2614,34 @@
         <v>54</v>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>121.5852</v>
+        <v>116.8544</v>
       </c>
       <c r="F7" t="n">
-        <v>130.7851</v>
+        <v>121.3464</v>
       </c>
       <c r="G7" t="n">
-        <v>121.081</v>
+        <v>118.0777</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7556</v>
+        <v>0.9087</v>
       </c>
       <c r="I7" t="n">
-        <v>127.0459</v>
+        <v>216.8799</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3156</v>
+        <v>0.0882</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.8404</v>
+        <v>-1.6637</v>
       </c>
       <c r="L7" t="s">
         <v>49</v>
@@ -2635,25 +2661,25 @@
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>116.8029</v>
+        <v>118.5641</v>
       </c>
       <c r="F8" t="n">
-        <v>124.3908</v>
+        <v>126.3749</v>
       </c>
       <c r="G8" t="n">
-        <v>117.9214</v>
+        <v>119.8374</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8413</v>
+        <v>0.835</v>
       </c>
       <c r="I8" t="n">
-        <v>210.3531</v>
+        <v>211.8569</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3142</v>
+        <v>0.2496</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.7725</v>
+        <v>-1.5822</v>
       </c>
       <c r="L8" t="s">
         <v>49</v>
@@ -2670,28 +2696,28 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E9" t="n">
-        <v>117.8819</v>
+        <v>122.7985</v>
       </c>
       <c r="F9" t="n">
-        <v>126.2041</v>
+        <v>132.4142</v>
       </c>
       <c r="G9" t="n">
-        <v>118.6565</v>
+        <v>122.608</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8172</v>
+        <v>0.761</v>
       </c>
       <c r="I9" t="n">
-        <v>241.5913</v>
+        <v>126.2774</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3986</v>
+        <v>0.3739</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.4606</v>
+        <v>-1.4913</v>
       </c>
       <c r="L9" t="s">
         <v>49</v>
@@ -2702,34 +2728,34 @@
         <v>57</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>116.8489</v>
+        <v>119.4846</v>
       </c>
       <c r="F10" t="n">
-        <v>122.4615</v>
+        <v>128.0856</v>
       </c>
       <c r="G10" t="n">
-        <v>118.1486</v>
+        <v>120.4586</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9095</v>
+        <v>0.8104</v>
       </c>
       <c r="I10" t="n">
-        <v>167.9541</v>
+        <v>237.0422</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1569</v>
+        <v>0.3328</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.3572</v>
+        <v>-1.3358</v>
       </c>
       <c r="L10" t="s">
         <v>49</v>
@@ -2740,34 +2766,34 @@
         <v>58</v>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E11" t="n">
-        <v>115.565</v>
+        <v>120.4684</v>
       </c>
       <c r="F11" t="n">
-        <v>118.6185</v>
+        <v>128.2792</v>
       </c>
       <c r="G11" t="n">
-        <v>116.462</v>
+        <v>121.7417</v>
       </c>
       <c r="H11" t="n">
-        <v>0.955</v>
+        <v>0.8423</v>
       </c>
       <c r="I11" t="n">
-        <v>216.8685</v>
+        <v>136.7912</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3141</v>
+        <v>0.1074</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.2451</v>
+        <v>-1.3057</v>
       </c>
       <c r="L11" t="s">
         <v>49</v>
@@ -2778,34 +2804,34 @@
         <v>59</v>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>116.968</v>
+        <v>118.785</v>
       </c>
       <c r="F12" t="n">
-        <v>122.5807</v>
+        <v>124.5282</v>
       </c>
       <c r="G12" t="n">
-        <v>118.2677</v>
+        <v>120.1699</v>
       </c>
       <c r="H12" t="n">
-        <v>0.911</v>
+        <v>0.9012</v>
       </c>
       <c r="I12" t="n">
-        <v>185.9967</v>
+        <v>155.6463</v>
       </c>
       <c r="J12" t="n">
-        <v>0.14</v>
+        <v>0.0959</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.1781</v>
+        <v>-1.2552</v>
       </c>
       <c r="L12" t="s">
         <v>49</v>
@@ -2816,34 +2842,34 @@
         <v>60</v>
       </c>
       <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="n">
         <v>2</v>
       </c>
-      <c r="C13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1</v>
-      </c>
       <c r="E13" t="n">
-        <v>116.9495</v>
+        <v>118.9156</v>
       </c>
       <c r="F13" t="n">
-        <v>122.5621</v>
+        <v>124.6588</v>
       </c>
       <c r="G13" t="n">
-        <v>118.2492</v>
+        <v>120.3005</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9113</v>
+        <v>0.9028</v>
       </c>
       <c r="I13" t="n">
-        <v>190.9877</v>
+        <v>176.5401</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1434</v>
+        <v>0.0759</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.1463</v>
+        <v>-1.0544</v>
       </c>
       <c r="L13" t="s">
         <v>49</v>
@@ -2854,34 +2880,34 @@
         <v>61</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>118.5861</v>
+        <v>118.8981</v>
       </c>
       <c r="F14" t="n">
-        <v>127.7947</v>
+        <v>124.6413</v>
       </c>
       <c r="G14" t="n">
-        <v>119.078</v>
+        <v>120.283</v>
       </c>
       <c r="H14" t="n">
-        <v>0.7579</v>
+        <v>0.9029</v>
       </c>
       <c r="I14" t="n">
-        <v>416.1484</v>
+        <v>177.6649</v>
       </c>
       <c r="J14" t="n">
-        <v>0.4924</v>
+        <v>0.0785</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.0438</v>
+        <v>-1.0524</v>
       </c>
       <c r="L14" t="s">
         <v>49</v>
@@ -2892,7 +2918,7 @@
         <v>62</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
         <v>1</v>
@@ -2901,25 +2927,25 @@
         <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>121.2188</v>
+        <v>121.306</v>
       </c>
       <c r="F15" t="n">
-        <v>129.541</v>
+        <v>129.1168</v>
       </c>
       <c r="G15" t="n">
-        <v>121.9933</v>
+        <v>122.5793</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8314</v>
+        <v>0.8334</v>
       </c>
       <c r="I15" t="n">
-        <v>128.8852</v>
+        <v>171.3363</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1688</v>
+        <v>0.1924</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.9253</v>
+        <v>-0.9521</v>
       </c>
       <c r="L15" t="s">
         <v>49</v>
@@ -2930,34 +2956,34 @@
         <v>63</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>118.7858</v>
+        <v>119.8938</v>
       </c>
       <c r="F16" t="n">
-        <v>125.4654</v>
+        <v>129.4316</v>
       </c>
       <c r="G16" t="n">
-        <v>120.0743</v>
+        <v>120.6256</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8991</v>
+        <v>0.76</v>
       </c>
       <c r="I16" t="n">
-        <v>143.5726</v>
+        <v>412.7161</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2962</v>
+        <v>0.4897</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.8505</v>
+        <v>-0.8596</v>
       </c>
       <c r="L16" t="s">
         <v>49</v>
@@ -2971,31 +2997,31 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E17" t="n">
-        <v>121.3408</v>
+        <v>121.2813</v>
       </c>
       <c r="F17" t="n">
-        <v>130.9565</v>
+        <v>129.0922</v>
       </c>
       <c r="G17" t="n">
-        <v>121.1502</v>
+        <v>122.5547</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7518</v>
+        <v>0.8514</v>
       </c>
       <c r="I17" t="n">
-        <v>336.0479</v>
+        <v>143.2282</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3629</v>
+        <v>0.085</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.7079</v>
+        <v>-0.8481</v>
       </c>
       <c r="L17" t="s">
         <v>49</v>
@@ -3006,7 +3032,7 @@
         <v>65</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
         <v>1</v>
@@ -3015,25 +3041,25 @@
         <v>3</v>
       </c>
       <c r="E18" t="n">
-        <v>119.4797</v>
+        <v>122.6822</v>
       </c>
       <c r="F18" t="n">
-        <v>127.0675</v>
+        <v>131.2833</v>
       </c>
       <c r="G18" t="n">
-        <v>120.5981</v>
+        <v>123.6562</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8716</v>
+        <v>0.8214</v>
       </c>
       <c r="I18" t="n">
-        <v>172.9731</v>
+        <v>123.9488</v>
       </c>
       <c r="J18" t="n">
-        <v>0.377</v>
+        <v>0.147</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.6915</v>
+        <v>-0.8101</v>
       </c>
       <c r="L18" t="s">
         <v>49</v>
@@ -3044,34 +3070,34 @@
         <v>66</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>114.4326</v>
+        <v>118.6854</v>
       </c>
       <c r="F19" t="n">
-        <v>118.9247</v>
+        <v>121.7968</v>
       </c>
       <c r="G19" t="n">
-        <v>115.656</v>
+        <v>119.6176</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8973</v>
+        <v>0.9615</v>
       </c>
       <c r="I19" t="n">
-        <v>497.8504</v>
+        <v>181.8376</v>
       </c>
       <c r="J19" t="n">
-        <v>0.2902</v>
+        <v>0.1009</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.5661</v>
+        <v>-0.7304</v>
       </c>
       <c r="L19" t="s">
         <v>49</v>
@@ -3082,34 +3108,34 @@
         <v>67</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E20" t="n">
-        <v>119.4186</v>
+        <v>121.0245</v>
       </c>
       <c r="F20" t="n">
-        <v>126.0983</v>
+        <v>127.878</v>
       </c>
       <c r="G20" t="n">
-        <v>120.7071</v>
+        <v>122.4301</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9085</v>
+        <v>0.8943</v>
       </c>
       <c r="I20" t="n">
-        <v>153.906</v>
+        <v>131.5932</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1207</v>
+        <v>0.1196</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.4347</v>
+        <v>-0.5312</v>
       </c>
       <c r="L20" t="s">
         <v>49</v>
@@ -3120,34 +3146,34 @@
         <v>68</v>
       </c>
       <c r="B21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E21" t="n">
-        <v>116.6406</v>
+        <v>122.5452</v>
       </c>
       <c r="F21" t="n">
-        <v>123.4941</v>
+        <v>132.5593</v>
       </c>
       <c r="G21" t="n">
-        <v>118.0462</v>
+        <v>122.6525</v>
       </c>
       <c r="H21" t="n">
-        <v>0.8478</v>
+        <v>0.7545</v>
       </c>
       <c r="I21" t="n">
-        <v>477.3937</v>
+        <v>327.7645</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1941</v>
+        <v>0.3754</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.314</v>
+        <v>-0.4941</v>
       </c>
       <c r="L21" t="s">
         <v>49</v>
@@ -3158,34 +3184,34 @@
         <v>69</v>
       </c>
       <c r="B22" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>122.8445</v>
+        <v>116.5103</v>
       </c>
       <c r="F22" t="n">
-        <v>131.7104</v>
+        <v>121.0917</v>
       </c>
       <c r="G22" t="n">
-        <v>123.0845</v>
+        <v>117.7895</v>
       </c>
       <c r="H22" t="n">
-        <v>0.8131</v>
+        <v>0.8914</v>
       </c>
       <c r="I22" t="n">
-        <v>173.3649</v>
+        <v>487.3698</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2548</v>
+        <v>0.1873</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.3014</v>
+        <v>-0.49</v>
       </c>
       <c r="L22" t="s">
         <v>49</v>
@@ -3196,34 +3222,34 @@
         <v>70</v>
       </c>
       <c r="B23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>118.3664</v>
+        <v>118.4515</v>
       </c>
       <c r="F23" t="n">
-        <v>123.979</v>
+        <v>125.4732</v>
       </c>
       <c r="G23" t="n">
-        <v>119.6661</v>
+        <v>119.9695</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9314</v>
+        <v>0.8406</v>
       </c>
       <c r="I23" t="n">
-        <v>210.8807</v>
+        <v>467.0112</v>
       </c>
       <c r="J23" t="n">
-        <v>0.1154</v>
+        <v>0.1466</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.2516</v>
+        <v>-0.2585</v>
       </c>
       <c r="L23" t="s">
         <v>49</v>
@@ -3240,28 +3266,28 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E24" t="n">
-        <v>118.4987</v>
+        <v>121.3678</v>
       </c>
       <c r="F24" t="n">
-        <v>121.5522</v>
+        <v>128.2214</v>
       </c>
       <c r="G24" t="n">
-        <v>119.3957</v>
+        <v>122.7734</v>
       </c>
       <c r="H24" t="n">
-        <v>0.9953</v>
+        <v>0.9008</v>
       </c>
       <c r="I24" t="n">
-        <v>137.8879</v>
+        <v>146.9118</v>
       </c>
       <c r="J24" t="n">
-        <v>0.1039</v>
+        <v>0.0677</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.1923</v>
+        <v>-0.2165</v>
       </c>
       <c r="L24" t="s">
         <v>49</v>
@@ -3272,34 +3298,34 @@
         <v>72</v>
       </c>
       <c r="B25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C25" t="n">
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>118.5606</v>
+        <v>124.2128</v>
       </c>
       <c r="F25" t="n">
-        <v>122.9606</v>
+        <v>133.4213</v>
       </c>
       <c r="G25" t="n">
-        <v>119.7259</v>
+        <v>124.7047</v>
       </c>
       <c r="H25" t="n">
-        <v>0.9658</v>
+        <v>0.8033</v>
       </c>
       <c r="I25" t="n">
-        <v>193.0838</v>
+        <v>166.4701</v>
       </c>
       <c r="J25" t="n">
-        <v>0.0581</v>
+        <v>0.2269</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.0083</v>
+        <v>-0.1861</v>
       </c>
       <c r="L25" t="s">
         <v>49</v>
@@ -3310,34 +3336,34 @@
         <v>73</v>
       </c>
       <c r="B26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C26" t="n">
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>119.5076</v>
+        <v>120.5113</v>
       </c>
       <c r="F26" t="n">
-        <v>126.1873</v>
+        <v>123.6227</v>
       </c>
       <c r="G26" t="n">
-        <v>120.7961</v>
+        <v>121.4435</v>
       </c>
       <c r="H26" t="n">
-        <v>0.9123</v>
+        <v>0.9857</v>
       </c>
       <c r="I26" t="n">
-        <v>212.8574</v>
+        <v>132.9251</v>
       </c>
       <c r="J26" t="n">
-        <v>0.1328</v>
+        <v>0.0832</v>
       </c>
       <c r="K26" t="n">
-        <v>0.0351</v>
+        <v>-0.0442</v>
       </c>
       <c r="L26" t="s">
         <v>49</v>
@@ -3348,34 +3374,34 @@
         <v>74</v>
       </c>
       <c r="B27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C27" t="n">
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>119.4651</v>
+        <v>121.5012</v>
       </c>
       <c r="F27" t="n">
-        <v>126.1448</v>
+        <v>128.3548</v>
       </c>
       <c r="G27" t="n">
-        <v>120.7536</v>
+        <v>122.9069</v>
       </c>
       <c r="H27" t="n">
-        <v>0.9119</v>
+        <v>0.9029</v>
       </c>
       <c r="I27" t="n">
-        <v>227.5652</v>
+        <v>177.553</v>
       </c>
       <c r="J27" t="n">
-        <v>0.1526</v>
+        <v>0.0508</v>
       </c>
       <c r="K27" t="n">
-        <v>0.1116</v>
+        <v>0.0549</v>
       </c>
       <c r="L27" t="s">
         <v>49</v>
@@ -3386,34 +3412,34 @@
         <v>75</v>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
         <v>4</v>
       </c>
       <c r="E28" t="n">
-        <v>121.5527</v>
+        <v>125.7815</v>
       </c>
       <c r="F28" t="n">
-        <v>129.1406</v>
+        <v>136.0614</v>
       </c>
       <c r="G28" t="n">
-        <v>122.6712</v>
+        <v>125.054</v>
       </c>
       <c r="H28" t="n">
-        <v>0.8985</v>
+        <v>0.7358</v>
       </c>
       <c r="I28" t="n">
-        <v>138.3222</v>
+        <v>323.4042</v>
       </c>
       <c r="J28" t="n">
-        <v>0.217</v>
+        <v>0.2129</v>
       </c>
       <c r="K28" t="n">
-        <v>0.1635</v>
+        <v>0.3184</v>
       </c>
       <c r="L28" t="s">
         <v>49</v>
@@ -3427,31 +3453,31 @@
         <v>4</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>124.72</v>
+        <v>121.5356</v>
       </c>
       <c r="F29" t="n">
-        <v>134.5224</v>
+        <v>128.3891</v>
       </c>
       <c r="G29" t="n">
-        <v>123.6265</v>
+        <v>122.9412</v>
       </c>
       <c r="H29" t="n">
-        <v>0.7445</v>
+        <v>0.9059</v>
       </c>
       <c r="I29" t="n">
-        <v>333.2798</v>
+        <v>217.0554</v>
       </c>
       <c r="J29" t="n">
-        <v>0.206</v>
+        <v>0.0885</v>
       </c>
       <c r="K29" t="n">
-        <v>0.2614</v>
+        <v>0.3628</v>
       </c>
       <c r="L29" t="s">
         <v>49</v>
@@ -3468,28 +3494,28 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>119.213</v>
+        <v>118.8348</v>
       </c>
       <c r="F30" t="n">
-        <v>127.0239</v>
+        <v>124.7044</v>
       </c>
       <c r="G30" t="n">
-        <v>120.4864</v>
+        <v>120.3014</v>
       </c>
       <c r="H30" t="n">
-        <v>0.8446</v>
+        <v>0.8901</v>
       </c>
       <c r="I30" t="n">
-        <v>448.2094</v>
+        <v>508.1338</v>
       </c>
       <c r="J30" t="n">
-        <v>0.1772</v>
+        <v>0.1133</v>
       </c>
       <c r="K30" t="n">
-        <v>0.4512</v>
+        <v>0.6698</v>
       </c>
       <c r="L30" t="s">
         <v>49</v>
@@ -3500,7 +3526,7 @@
         <v>78</v>
       </c>
       <c r="B31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
@@ -3509,25 +3535,25 @@
         <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>119.2053</v>
+        <v>118.822</v>
       </c>
       <c r="F31" t="n">
-        <v>127.0161</v>
+        <v>124.6916</v>
       </c>
       <c r="G31" t="n">
-        <v>120.4786</v>
+        <v>120.2886</v>
       </c>
       <c r="H31" t="n">
-        <v>0.8444</v>
+        <v>0.8899</v>
       </c>
       <c r="I31" t="n">
-        <v>451.3057</v>
+        <v>509.6397</v>
       </c>
       <c r="J31" t="n">
-        <v>0.1814</v>
+        <v>0.1082</v>
       </c>
       <c r="K31" t="n">
-        <v>0.4655</v>
+        <v>0.6728</v>
       </c>
       <c r="L31" t="s">
         <v>49</v>
@@ -3538,34 +3564,34 @@
         <v>79</v>
       </c>
       <c r="B32" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" t="n">
         <v>2</v>
       </c>
-      <c r="C32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" t="n">
-        <v>0</v>
-      </c>
       <c r="E32" t="n">
-        <v>116.8603</v>
+        <v>118.8487</v>
       </c>
       <c r="F32" t="n">
-        <v>122.6035</v>
+        <v>124.7183</v>
       </c>
       <c r="G32" t="n">
-        <v>118.2451</v>
+        <v>120.3153</v>
       </c>
       <c r="H32" t="n">
-        <v>0.8969</v>
+        <v>0.8897</v>
       </c>
       <c r="I32" t="n">
-        <v>509.5951</v>
+        <v>510.035</v>
       </c>
       <c r="J32" t="n">
-        <v>0.1969</v>
+        <v>0.1386</v>
       </c>
       <c r="K32" t="n">
-        <v>0.5226</v>
+        <v>0.6798</v>
       </c>
       <c r="L32" t="s">
         <v>49</v>
@@ -3576,7 +3602,7 @@
         <v>80</v>
       </c>
       <c r="B33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C33" t="n">
         <v>0</v>
@@ -3585,25 +3611,25 @@
         <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>116.8528</v>
+        <v>121.0956</v>
       </c>
       <c r="F33" t="n">
-        <v>122.596</v>
+        <v>129.1216</v>
       </c>
       <c r="G33" t="n">
-        <v>118.2377</v>
+        <v>122.5172</v>
       </c>
       <c r="H33" t="n">
-        <v>0.8968</v>
+        <v>0.8388</v>
       </c>
       <c r="I33" t="n">
-        <v>511.7845</v>
+        <v>450.2961</v>
       </c>
       <c r="J33" t="n">
-        <v>0.1916</v>
+        <v>0.1182</v>
       </c>
       <c r="K33" t="n">
-        <v>0.533</v>
+        <v>0.7051</v>
       </c>
       <c r="L33" t="s">
         <v>49</v>
@@ -3614,7 +3640,7 @@
         <v>81</v>
       </c>
       <c r="B34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C34" t="n">
         <v>0</v>
@@ -3623,25 +3649,25 @@
         <v>2</v>
       </c>
       <c r="E34" t="n">
-        <v>116.9289</v>
+        <v>121.112</v>
       </c>
       <c r="F34" t="n">
-        <v>122.6721</v>
+        <v>129.138</v>
       </c>
       <c r="G34" t="n">
-        <v>118.3138</v>
+        <v>122.5336</v>
       </c>
       <c r="H34" t="n">
-        <v>0.8971</v>
+        <v>0.8392</v>
       </c>
       <c r="I34" t="n">
-        <v>520.5967</v>
+        <v>452.2966</v>
       </c>
       <c r="J34" t="n">
-        <v>0.2019</v>
+        <v>0.1126</v>
       </c>
       <c r="K34" t="n">
-        <v>0.6189</v>
+        <v>0.7287</v>
       </c>
       <c r="L34" t="s">
         <v>49</v>
@@ -3652,34 +3678,34 @@
         <v>82</v>
       </c>
       <c r="B35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E35" t="n">
-        <v>122.2863</v>
+        <v>122.0289</v>
       </c>
       <c r="F35" t="n">
-        <v>129.8741</v>
+        <v>130.8984</v>
       </c>
       <c r="G35" t="n">
-        <v>123.4047</v>
+        <v>123.1932</v>
       </c>
       <c r="H35" t="n">
-        <v>0.9122</v>
+        <v>0.8152</v>
       </c>
       <c r="I35" t="n">
-        <v>210.799</v>
+        <v>458.9521</v>
       </c>
       <c r="J35" t="n">
-        <v>0.0857</v>
+        <v>0.1264</v>
       </c>
       <c r="K35" t="n">
-        <v>1.0825</v>
+        <v>0.8771</v>
       </c>
       <c r="L35" t="s">
         <v>49</v>
@@ -3699,25 +3725,25 @@
         <v>3</v>
       </c>
       <c r="E36" t="n">
-        <v>118.6962</v>
+        <v>120.3012</v>
       </c>
       <c r="F36" t="n">
-        <v>125.5498</v>
+        <v>127.3229</v>
       </c>
       <c r="G36" t="n">
-        <v>120.1019</v>
+        <v>121.8192</v>
       </c>
       <c r="H36" t="n">
-        <v>0.8815</v>
+        <v>0.8717</v>
       </c>
       <c r="I36" t="n">
-        <v>512.1425</v>
+        <v>498.6496</v>
       </c>
       <c r="J36" t="n">
-        <v>0.1155</v>
+        <v>0.0938</v>
       </c>
       <c r="K36" t="n">
-        <v>1.0975</v>
+        <v>1.0535</v>
       </c>
       <c r="L36" t="s">
         <v>49</v>
@@ -3737,25 +3763,25 @@
         <v>2</v>
       </c>
       <c r="E37" t="n">
-        <v>119.1196</v>
+        <v>121.2521</v>
       </c>
       <c r="F37" t="n">
-        <v>125.9731</v>
+        <v>128.2738</v>
       </c>
       <c r="G37" t="n">
-        <v>120.5252</v>
+        <v>122.77</v>
       </c>
       <c r="H37" t="n">
-        <v>0.8929</v>
+        <v>0.8881</v>
       </c>
       <c r="I37" t="n">
-        <v>470.4294</v>
+        <v>483.9159</v>
       </c>
       <c r="J37" t="n">
-        <v>0.1342</v>
+        <v>0.0548</v>
       </c>
       <c r="K37" t="n">
-        <v>1.1428</v>
+        <v>1.5388</v>
       </c>
       <c r="L37" t="s">
         <v>49</v>
@@ -3766,34 +3792,34 @@
         <v>85</v>
       </c>
       <c r="B38" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>121.9416</v>
+        <v>118.2274</v>
       </c>
       <c r="F38" t="n">
-        <v>130.5427</v>
+        <v>122.8088</v>
       </c>
       <c r="G38" t="n">
-        <v>122.9156</v>
+        <v>119.5066</v>
       </c>
       <c r="H38" t="n">
-        <v>0.8427</v>
+        <v>0.91</v>
       </c>
       <c r="I38" t="n">
-        <v>419.2227</v>
+        <v>683.8865</v>
       </c>
       <c r="J38" t="n">
-        <v>0.1178</v>
+        <v>0.069</v>
       </c>
       <c r="K38" t="n">
-        <v>1.2557</v>
+        <v>1.6161</v>
       </c>
       <c r="L38" t="s">
         <v>49</v>
@@ -3804,34 +3830,34 @@
         <v>86</v>
       </c>
       <c r="B39" t="n">
+        <v>3</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" t="n">
         <v>2</v>
       </c>
-      <c r="C39" t="n">
-        <v>0</v>
-      </c>
-      <c r="D39" t="n">
-        <v>3</v>
-      </c>
       <c r="E39" t="n">
-        <v>122.0301</v>
+        <v>123.8893</v>
       </c>
       <c r="F39" t="n">
-        <v>130.6311</v>
+        <v>132.7589</v>
       </c>
       <c r="G39" t="n">
-        <v>123.004</v>
+        <v>125.0536</v>
       </c>
       <c r="H39" t="n">
-        <v>0.8436</v>
+        <v>0.838</v>
       </c>
       <c r="I39" t="n">
-        <v>425.6287</v>
+        <v>426.1186</v>
       </c>
       <c r="J39" t="n">
-        <v>0.1187</v>
+        <v>0.0678</v>
       </c>
       <c r="K39" t="n">
-        <v>1.338</v>
+        <v>1.6534</v>
       </c>
       <c r="L39" t="s">
         <v>49</v>
@@ -3842,34 +3868,34 @@
         <v>87</v>
       </c>
       <c r="B40" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C40" t="n">
         <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E40" t="n">
-        <v>119.3483</v>
+        <v>125.1219</v>
       </c>
       <c r="F40" t="n">
-        <v>126.2019</v>
+        <v>134.6596</v>
       </c>
       <c r="G40" t="n">
-        <v>120.754</v>
+        <v>125.8536</v>
       </c>
       <c r="H40" t="n">
-        <v>0.8956</v>
+        <v>0.8056</v>
       </c>
       <c r="I40" t="n">
-        <v>506.1772</v>
+        <v>432.5871</v>
       </c>
       <c r="J40" t="n">
-        <v>0.1191</v>
+        <v>0.148</v>
       </c>
       <c r="K40" t="n">
-        <v>1.4892</v>
+        <v>1.7323</v>
       </c>
       <c r="L40" t="s">
         <v>49</v>
@@ -3880,34 +3906,34 @@
         <v>88</v>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>116.2819</v>
+        <v>121.3604</v>
       </c>
       <c r="F41" t="n">
-        <v>120.7739</v>
+        <v>128.3821</v>
       </c>
       <c r="G41" t="n">
-        <v>117.5052</v>
+        <v>122.8783</v>
       </c>
       <c r="H41" t="n">
-        <v>0.9181</v>
+        <v>0.8894</v>
       </c>
       <c r="I41" t="n">
-        <v>693.1461</v>
+        <v>506.2569</v>
       </c>
       <c r="J41" t="n">
-        <v>0.1136</v>
+        <v>0.0609</v>
       </c>
       <c r="K41" t="n">
-        <v>1.6104</v>
+        <v>1.7365</v>
       </c>
       <c r="L41" t="s">
         <v>49</v>
@@ -3918,34 +3944,34 @@
         <v>89</v>
       </c>
       <c r="B42" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>123.7907</v>
+        <v>119.9148</v>
       </c>
       <c r="F42" t="n">
-        <v>132.9992</v>
+        <v>121.5258</v>
       </c>
       <c r="G42" t="n">
-        <v>124.2826</v>
+        <v>120.4362</v>
       </c>
       <c r="H42" t="n">
-        <v>0.8156</v>
+        <v>1.0058</v>
       </c>
       <c r="I42" t="n">
-        <v>442.9264</v>
+        <v>140.4425</v>
       </c>
       <c r="J42" t="n">
-        <v>0.1603</v>
+        <v>0.0423</v>
       </c>
       <c r="K42" t="n">
-        <v>1.6808</v>
+        <v>1.8021</v>
       </c>
       <c r="L42" t="s">
         <v>49</v>
@@ -3959,31 +3985,31 @@
         <v>0</v>
       </c>
       <c r="C43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E43" t="n">
-        <v>118.0316</v>
+        <v>122.3112</v>
       </c>
       <c r="F43" t="n">
-        <v>119.6152</v>
+        <v>130.3372</v>
       </c>
       <c r="G43" t="n">
-        <v>118.537</v>
+        <v>123.7328</v>
       </c>
       <c r="H43" t="n">
-        <v>1.018</v>
+        <v>0.8641</v>
       </c>
       <c r="I43" t="n">
-        <v>143.853</v>
+        <v>512.0715</v>
       </c>
       <c r="J43" t="n">
-        <v>0.0472</v>
+        <v>0.0936</v>
       </c>
       <c r="K43" t="n">
-        <v>1.7584</v>
+        <v>1.9021</v>
       </c>
       <c r="L43" t="s">
         <v>49</v>
@@ -3994,34 +4020,34 @@
         <v>91</v>
       </c>
       <c r="B44" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D44" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>122.9958</v>
+        <v>120.9253</v>
       </c>
       <c r="F44" t="n">
-        <v>131.5969</v>
+        <v>126.6684</v>
       </c>
       <c r="G44" t="n">
-        <v>123.9698</v>
+        <v>122.3101</v>
       </c>
       <c r="H44" t="n">
-        <v>0.8653</v>
+        <v>0.931</v>
       </c>
       <c r="I44" t="n">
-        <v>408.3604</v>
+        <v>196.0455</v>
       </c>
       <c r="J44" t="n">
-        <v>0.3355</v>
+        <v>0.0302</v>
       </c>
       <c r="K44" t="n">
-        <v>1.8786</v>
+        <v>2.1867</v>
       </c>
       <c r="L44" t="s">
         <v>49</v>
@@ -4032,34 +4058,34 @@
         <v>92</v>
       </c>
       <c r="B45" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>121.459</v>
+        <v>120.7613</v>
       </c>
       <c r="F45" t="n">
-        <v>129.2698</v>
+        <v>125.2534</v>
       </c>
       <c r="G45" t="n">
-        <v>122.7323</v>
+        <v>121.9846</v>
       </c>
       <c r="H45" t="n">
-        <v>0.8879</v>
+        <v>0.9597</v>
       </c>
       <c r="I45" t="n">
-        <v>462.0424</v>
+        <v>183.1442</v>
       </c>
       <c r="J45" t="n">
-        <v>0.0995</v>
+        <v>0.0281</v>
       </c>
       <c r="K45" t="n">
-        <v>1.9413</v>
+        <v>2.2383</v>
       </c>
       <c r="L45" t="s">
         <v>49</v>
@@ -4070,7 +4096,7 @@
         <v>93</v>
       </c>
       <c r="B46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C46" t="n">
         <v>0</v>
@@ -4079,25 +4105,25 @@
         <v>4</v>
       </c>
       <c r="E46" t="n">
-        <v>121.6583</v>
+        <v>126.1654</v>
       </c>
       <c r="F46" t="n">
-        <v>129.4692</v>
+        <v>135.7031</v>
       </c>
       <c r="G46" t="n">
-        <v>122.9317</v>
+        <v>126.8972</v>
       </c>
       <c r="H46" t="n">
-        <v>0.8832</v>
+        <v>0.8292</v>
       </c>
       <c r="I46" t="n">
-        <v>470.5024</v>
+        <v>399.5383</v>
       </c>
       <c r="J46" t="n">
-        <v>0.3021</v>
+        <v>0.0542</v>
       </c>
       <c r="K46" t="n">
-        <v>1.9822</v>
+        <v>2.2494</v>
       </c>
       <c r="L46" t="s">
         <v>49</v>
@@ -4108,34 +4134,34 @@
         <v>94</v>
       </c>
       <c r="B47" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C47" t="n">
         <v>0</v>
       </c>
       <c r="D47" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E47" t="n">
-        <v>124.5387</v>
+        <v>128.6523</v>
       </c>
       <c r="F47" t="n">
-        <v>133.7473</v>
+        <v>138.6663</v>
       </c>
       <c r="G47" t="n">
-        <v>125.0306</v>
+        <v>128.7596</v>
       </c>
       <c r="H47" t="n">
-        <v>0.837</v>
+        <v>0.8077</v>
       </c>
       <c r="I47" t="n">
-        <v>401.6212</v>
+        <v>394.4096</v>
       </c>
       <c r="J47" t="n">
-        <v>0.0713</v>
+        <v>0.0659</v>
       </c>
       <c r="K47" t="n">
-        <v>1.9927</v>
+        <v>2.8071</v>
       </c>
       <c r="L47" t="s">
         <v>49</v>
@@ -4155,25 +4181,25 @@
         <v>3</v>
       </c>
       <c r="E48" t="n">
-        <v>122.1792</v>
+        <v>123.819</v>
       </c>
       <c r="F48" t="n">
-        <v>129.9901</v>
+        <v>131.845</v>
       </c>
       <c r="G48" t="n">
-        <v>123.4526</v>
+        <v>125.2405</v>
       </c>
       <c r="H48" t="n">
-        <v>0.8931</v>
+        <v>0.8863</v>
       </c>
       <c r="I48" t="n">
-        <v>501.5676</v>
+        <v>452.6896</v>
       </c>
       <c r="J48" t="n">
-        <v>0.1333</v>
+        <v>0.0499</v>
       </c>
       <c r="K48" t="n">
-        <v>2.5054</v>
+        <v>4.3847</v>
       </c>
       <c r="L48" t="s">
         <v>49</v>
@@ -4190,28 +4216,28 @@
         <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>127.2258</v>
+        <v>123.6496</v>
       </c>
       <c r="F49" t="n">
-        <v>136.8415</v>
+        <v>131.6757</v>
       </c>
       <c r="G49" t="n">
-        <v>127.0352</v>
+        <v>125.0712</v>
       </c>
       <c r="H49" t="n">
-        <v>0.8167</v>
+        <v>0.8843</v>
       </c>
       <c r="I49" t="n">
-        <v>397.4369</v>
+        <v>472.1438</v>
       </c>
       <c r="J49" t="n">
-        <v>0.0971</v>
+        <v>0.0362</v>
       </c>
       <c r="K49" t="n">
-        <v>2.5698</v>
+        <v>4.4192</v>
       </c>
       <c r="L49" t="s">
         <v>49</v>
@@ -4231,25 +4257,25 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>124.188</v>
+        <v>126.3095</v>
       </c>
       <c r="F50" t="n">
-        <v>132.7891</v>
+        <v>135.1791</v>
       </c>
       <c r="G50" t="n">
-        <v>125.162</v>
+        <v>127.4739</v>
       </c>
       <c r="H50" t="n">
-        <v>0.8856</v>
+        <v>0.8815</v>
       </c>
       <c r="I50" t="n">
-        <v>444.1797</v>
+        <v>450.2096</v>
       </c>
       <c r="J50" t="n">
-        <v>0.0733</v>
+        <v>0.0272</v>
       </c>
       <c r="K50" t="n">
-        <v>2.8095</v>
+        <v>5.3062</v>
       </c>
       <c r="L50" t="s">
         <v>49</v>
@@ -4306,7 +4332,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B2" t="n">
         <v>1</v>
@@ -4318,25 +4344,25 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-254.8752</v>
+        <v>-261.9645</v>
       </c>
       <c r="F2" t="n">
-        <v>-251.8218</v>
+        <v>-258.8532</v>
       </c>
       <c r="G2" t="n">
-        <v>-253.9783</v>
+        <v>-261.0323</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0093</v>
+        <v>0.0092</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1222</v>
+        <v>0.122</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0862</v>
+        <v>0.0599</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.6229</v>
+        <v>-1.5985</v>
       </c>
       <c r="L2" t="s">
         <v>98</v>
@@ -4356,25 +4382,25 @@
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>-253.2579</v>
+        <v>-259.8808</v>
       </c>
       <c r="F3" t="n">
-        <v>-248.858</v>
+        <v>-255.3888</v>
       </c>
       <c r="G3" t="n">
-        <v>-252.0927</v>
+        <v>-258.6575</v>
       </c>
       <c r="H3" t="n">
         <v>0.0092</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1204</v>
+        <v>0.121</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1488</v>
+        <v>0.0641</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.4202</v>
+        <v>-1.3702</v>
       </c>
       <c r="L3" t="s">
         <v>98</v>
@@ -4382,7 +4408,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="B4" t="n">
         <v>2</v>
@@ -4394,25 +4420,25 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-252.8271</v>
+        <v>-259.774</v>
       </c>
       <c r="F4" t="n">
-        <v>-248.4272</v>
+        <v>-255.282</v>
       </c>
       <c r="G4" t="n">
-        <v>-251.6619</v>
+        <v>-258.5507</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0093</v>
+        <v>0.0092</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1199</v>
+        <v>0.1203</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0947</v>
+        <v>0.0556</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.4028</v>
+        <v>-1.369</v>
       </c>
       <c r="L4" t="s">
         <v>98</v>
@@ -4420,37 +4446,37 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="B5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
         <v>2</v>
       </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
       <c r="E5" t="n">
-        <v>-251.1965</v>
+        <v>-256.3721</v>
       </c>
       <c r="F5" t="n">
-        <v>-245.4533</v>
+        <v>-251.88</v>
       </c>
       <c r="G5" t="n">
-        <v>-249.8116</v>
+        <v>-255.1488</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0094</v>
+        <v>0.0096</v>
       </c>
       <c r="I5" t="n">
-        <v>0.122</v>
+        <v>0.1332</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0599</v>
+        <v>0.0603</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.3088</v>
+        <v>-1.1454</v>
       </c>
       <c r="L5" t="s">
         <v>98</v>
@@ -4458,10 +4484,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
         <v>1</v>
@@ -4470,25 +4496,25 @@
         <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>-253.0543</v>
+        <v>-259.1463</v>
       </c>
       <c r="F6" t="n">
-        <v>-247.4417</v>
+        <v>-252.2927</v>
       </c>
       <c r="G6" t="n">
-        <v>-251.7546</v>
+        <v>-257.7406</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0089</v>
+        <v>0.0086</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1183</v>
+        <v>0.1209</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1152</v>
+        <v>0.0754</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.2892</v>
+        <v>-1.0773</v>
       </c>
       <c r="L6" t="s">
         <v>98</v>
@@ -4496,37 +4522,37 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>-252.7765</v>
+        <v>-256.3087</v>
       </c>
       <c r="F7" t="n">
-        <v>-247.1639</v>
+        <v>-250.5655</v>
       </c>
       <c r="G7" t="n">
-        <v>-251.4768</v>
+        <v>-254.9238</v>
       </c>
       <c r="H7" t="n">
-        <v>0.009</v>
+        <v>0.0093</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1175</v>
+        <v>0.1281</v>
       </c>
       <c r="J7" t="n">
-        <v>0.152</v>
+        <v>0.0657</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.2814</v>
+        <v>-1.0397</v>
       </c>
       <c r="L7" t="s">
         <v>98</v>
@@ -4534,37 +4560,37 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>-249.4651</v>
+        <v>-258.061</v>
       </c>
       <c r="F8" t="n">
-        <v>-245.0651</v>
+        <v>-251.2074</v>
       </c>
       <c r="G8" t="n">
-        <v>-248.2998</v>
+        <v>-256.6553</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0097</v>
+        <v>0.0088</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1325</v>
+        <v>0.1222</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0889</v>
+        <v>0.0583</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.1743</v>
+        <v>-1.022</v>
       </c>
       <c r="L8" t="s">
         <v>98</v>
@@ -4572,10 +4598,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
         <v>1</v>
@@ -4584,25 +4610,25 @@
         <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>-252.4253</v>
+        <v>-257.4496</v>
       </c>
       <c r="F9" t="n">
-        <v>-245.7456</v>
+        <v>-249.6388</v>
       </c>
       <c r="G9" t="n">
-        <v>-251.1368</v>
+        <v>-256.1763</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0086</v>
+        <v>0.0085</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1187</v>
+        <v>0.1157</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2061</v>
+        <v>0.0623</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.1433</v>
+        <v>-0.9114</v>
       </c>
       <c r="L9" t="s">
         <v>98</v>
@@ -4610,37 +4636,37 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="B10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
         <v>3</v>
       </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
       <c r="E10" t="n">
-        <v>-248.9663</v>
+        <v>-257.0706</v>
       </c>
       <c r="F10" t="n">
-        <v>-242.1128</v>
+        <v>-249.2598</v>
       </c>
       <c r="G10" t="n">
-        <v>-247.5607</v>
+        <v>-255.7973</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0093</v>
+        <v>0.0085</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1193</v>
+        <v>0.1175</v>
       </c>
       <c r="J10" t="n">
-        <v>0.067</v>
+        <v>0.0511</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.0904</v>
+        <v>-0.8792</v>
       </c>
       <c r="L10" t="s">
         <v>98</v>
@@ -4648,7 +4674,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="B11" t="n">
         <v>3</v>
@@ -4657,28 +4683,28 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E11" t="n">
-        <v>-250.9631</v>
+        <v>-259.3338</v>
       </c>
       <c r="F11" t="n">
-        <v>-244.2834</v>
+        <v>-250.1252</v>
       </c>
       <c r="G11" t="n">
-        <v>-249.6746</v>
+        <v>-258.8419</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0087</v>
+        <v>0.0075</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1204</v>
+        <v>0.1041</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0968</v>
+        <v>0.3692</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.0737</v>
+        <v>-0.8273</v>
       </c>
       <c r="L11" t="s">
         <v>98</v>
@@ -4686,37 +4712,37 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E12" t="n">
-        <v>-248.8705</v>
+        <v>-255.6156</v>
       </c>
       <c r="F12" t="n">
-        <v>-243.2578</v>
+        <v>-247.8047</v>
       </c>
       <c r="G12" t="n">
-        <v>-247.5708</v>
+        <v>-254.3423</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0094</v>
+        <v>0.0087</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1295</v>
+        <v>0.1167</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0887</v>
+        <v>0.0664</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.0356</v>
+        <v>-0.8161</v>
       </c>
       <c r="L12" t="s">
         <v>98</v>
@@ -4724,37 +4750,37 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="B13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="n">
         <v>4</v>
       </c>
-      <c r="C13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
       <c r="E13" t="n">
-        <v>-250.3216</v>
+        <v>-252.8761</v>
       </c>
       <c r="F13" t="n">
-        <v>-243.6419</v>
+        <v>-246.0225</v>
       </c>
       <c r="G13" t="n">
-        <v>-249.033</v>
+        <v>-251.4704</v>
       </c>
       <c r="H13" t="n">
-        <v>0.009</v>
+        <v>0.0093</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1198</v>
+        <v>0.1291</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0647</v>
+        <v>0.1598</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.0252</v>
+        <v>-0.7573</v>
       </c>
       <c r="L13" t="s">
         <v>98</v>
@@ -4762,37 +4788,37 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E14" t="n">
-        <v>-250.3327</v>
+        <v>-255.3384</v>
       </c>
       <c r="F14" t="n">
-        <v>-242.7449</v>
+        <v>-246.7373</v>
       </c>
       <c r="G14" t="n">
-        <v>-249.2143</v>
+        <v>-254.3644</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0085</v>
+        <v>0.0083</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1152</v>
+        <v>0.1133</v>
       </c>
       <c r="J14" t="n">
-        <v>0.1135</v>
+        <v>0.05</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.9487</v>
+        <v>-0.7143</v>
       </c>
       <c r="L14" t="s">
         <v>98</v>
@@ -4800,37 +4826,37 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="B15" t="n">
+        <v>4</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
         <v>2</v>
       </c>
-      <c r="C15" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" t="n">
-        <v>3</v>
-      </c>
       <c r="E15" t="n">
-        <v>-250.1954</v>
+        <v>-253.3979</v>
       </c>
       <c r="F15" t="n">
-        <v>-242.6076</v>
+        <v>-244.7969</v>
       </c>
       <c r="G15" t="n">
-        <v>-249.077</v>
+        <v>-252.424</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0085</v>
+        <v>0.0084</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1155</v>
+        <v>0.109</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1172</v>
+        <v>0.0525</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.9407</v>
+        <v>-0.6661</v>
       </c>
       <c r="L15" t="s">
         <v>98</v>
@@ -4838,37 +4864,37 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>-249.2413</v>
+        <v>-255.824</v>
       </c>
       <c r="F16" t="n">
-        <v>-241.6534</v>
+        <v>-246.6154</v>
       </c>
       <c r="G16" t="n">
-        <v>-248.1228</v>
+        <v>-255.3321</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0087</v>
+        <v>0.0077</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1143</v>
+        <v>0.1102</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2427</v>
+        <v>0.0568</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.8898</v>
+        <v>-0.6596</v>
       </c>
       <c r="L16" t="s">
         <v>98</v>
@@ -4876,37 +4902,37 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E17" t="n">
-        <v>-249.7414</v>
+        <v>-256.1912</v>
       </c>
       <c r="F17" t="n">
-        <v>-240.5329</v>
+        <v>-246.5755</v>
       </c>
       <c r="G17" t="n">
-        <v>-249.2495</v>
+        <v>-256.3818</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0078</v>
+        <v>0.0074</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1125</v>
+        <v>0.1007</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0723</v>
+        <v>0.2412</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.8513</v>
+        <v>-0.6158</v>
       </c>
       <c r="L17" t="s">
         <v>98</v>
@@ -4914,37 +4940,37 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="B18" t="n">
         <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E18" t="n">
-        <v>-251.3408</v>
+        <v>-251.3366</v>
       </c>
       <c r="F18" t="n">
-        <v>-242.4749</v>
+        <v>-241.7988</v>
       </c>
       <c r="G18" t="n">
-        <v>-251.1008</v>
+        <v>-250.6048</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0076</v>
+        <v>0.0083</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1049</v>
+        <v>0.1143</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3249</v>
+        <v>0.2825</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.8339</v>
+        <v>-0.5731</v>
       </c>
       <c r="L18" t="s">
         <v>98</v>
@@ -4952,37 +4978,37 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="B19" t="n">
         <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>-248.2941</v>
+        <v>-251.7521</v>
       </c>
       <c r="F19" t="n">
-        <v>-240.7063</v>
+        <v>-241.7381</v>
       </c>
       <c r="G19" t="n">
-        <v>-247.1757</v>
+        <v>-251.6448</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0089</v>
+        <v>0.0082</v>
       </c>
       <c r="I19" t="n">
-        <v>0.12</v>
+        <v>0.1103</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0683</v>
+        <v>0.0862</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.8062</v>
+        <v>-0.4655</v>
       </c>
       <c r="L19" t="s">
         <v>98</v>
@@ -4990,37 +5016,37 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
         <v>4</v>
       </c>
       <c r="E20" t="n">
-        <v>-245.9459</v>
+        <v>-250.4823</v>
       </c>
       <c r="F20" t="n">
-        <v>-239.2662</v>
+        <v>-240.4683</v>
       </c>
       <c r="G20" t="n">
-        <v>-244.6573</v>
+        <v>-250.375</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0094</v>
+        <v>0.0083</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1287</v>
+        <v>0.1149</v>
       </c>
       <c r="J20" t="n">
-        <v>0.2054</v>
+        <v>0.243</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.7788</v>
+        <v>-0.3886</v>
       </c>
       <c r="L20" t="s">
         <v>98</v>
@@ -5028,37 +5054,37 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="B21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>-246.5465</v>
+        <v>-263.7335</v>
       </c>
       <c r="F21" t="n">
-        <v>-237.9454</v>
+        <v>-257.8639</v>
       </c>
       <c r="G21" t="n">
-        <v>-245.5725</v>
+        <v>-262.2669</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0087</v>
+        <v>0.0092</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1201</v>
+        <v>0.1205</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0523</v>
+        <v>0.0234</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.7544</v>
+        <v>0.52</v>
       </c>
       <c r="L21" t="s">
         <v>98</v>
@@ -5066,37 +5092,37 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="B22" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C22" t="n">
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E22" t="n">
-        <v>-248.3138</v>
+        <v>-259.8931</v>
       </c>
       <c r="F22" t="n">
-        <v>-239.4479</v>
+        <v>-254.1499</v>
       </c>
       <c r="G22" t="n">
-        <v>-248.0738</v>
+        <v>-258.5083</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0078</v>
+        <v>0.0089</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1101</v>
+        <v>0.1197</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0658</v>
+        <v>0.0397</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.6805</v>
+        <v>0.7573</v>
       </c>
       <c r="L22" t="s">
         <v>98</v>
@@ -5104,37 +5130,37 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>48</v>
+        <v>91</v>
       </c>
       <c r="B23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C23" t="n">
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>-246.2902</v>
+        <v>-258.0648</v>
       </c>
       <c r="F23" t="n">
-        <v>-237.968</v>
+        <v>-252.3216</v>
       </c>
       <c r="G23" t="n">
-        <v>-245.5157</v>
+        <v>-256.6799</v>
       </c>
       <c r="H23" t="n">
-        <v>0.0087</v>
+        <v>0.0091</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1145</v>
+        <v>0.1218</v>
       </c>
       <c r="J23" t="n">
-        <v>0.161</v>
+        <v>0.0179</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.6345</v>
+        <v>0.8521</v>
       </c>
       <c r="L23" t="s">
         <v>98</v>
@@ -5142,37 +5168,37 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>54</v>
+        <v>81</v>
       </c>
       <c r="B24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>-248.0891</v>
+        <v>-259.8563</v>
       </c>
       <c r="F24" t="n">
-        <v>-238.8892</v>
+        <v>-251.8302</v>
       </c>
       <c r="G24" t="n">
-        <v>-248.5933</v>
+        <v>-258.4347</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0075</v>
+        <v>0.0083</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1034</v>
+        <v>0.1199</v>
       </c>
       <c r="J24" t="n">
-        <v>0.2064</v>
+        <v>0.0127</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.5975</v>
+        <v>0.8684</v>
       </c>
       <c r="L24" t="s">
         <v>98</v>
@@ -5180,37 +5206,37 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>89</v>
+        <v>61</v>
       </c>
       <c r="B25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>-243.7104</v>
+        <v>-257.1693</v>
       </c>
       <c r="F25" t="n">
-        <v>-234.5018</v>
+        <v>-251.4261</v>
       </c>
       <c r="G25" t="n">
-        <v>-243.2185</v>
+        <v>-255.7844</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0086</v>
+        <v>0.0092</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1095</v>
+        <v>0.1221</v>
       </c>
       <c r="J25" t="n">
-        <v>0.0516</v>
+        <v>0.0244</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.5863</v>
+        <v>0.8942</v>
       </c>
       <c r="L25" t="s">
         <v>98</v>
@@ -5218,37 +5244,37 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>-242.5769</v>
+        <v>-253.3437</v>
       </c>
       <c r="F26" t="n">
-        <v>-232.9612</v>
+        <v>-250.2323</v>
       </c>
       <c r="G26" t="n">
-        <v>-242.7675</v>
+        <v>-252.4115</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0084</v>
+        <v>0.0103</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1174</v>
+        <v>0.1447</v>
       </c>
       <c r="J26" t="n">
-        <v>0.2582</v>
+        <v>0.0033</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.3685</v>
+        <v>0.9189</v>
       </c>
       <c r="L26" t="s">
         <v>98</v>
@@ -5256,10 +5282,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="B27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C27" t="n">
         <v>1</v>
@@ -5268,25 +5294,25 @@
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>-251.2663</v>
+        <v>-256.8079</v>
       </c>
       <c r="F27" t="n">
-        <v>-245.6536</v>
+        <v>-249.9543</v>
       </c>
       <c r="G27" t="n">
-        <v>-249.9666</v>
+        <v>-255.4022</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0092</v>
+        <v>0.009</v>
       </c>
       <c r="I27" t="n">
-        <v>0.121</v>
+        <v>0.1216</v>
       </c>
       <c r="J27" t="n">
-        <v>0.046</v>
+        <v>0.0139</v>
       </c>
       <c r="K27" t="n">
-        <v>0.8099</v>
+        <v>1.0383</v>
       </c>
       <c r="L27" t="s">
         <v>98</v>
@@ -5294,37 +5320,37 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
         <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>-246.3154</v>
+        <v>-254.8631</v>
       </c>
       <c r="F28" t="n">
-        <v>-243.262</v>
+        <v>-248.9935</v>
       </c>
       <c r="G28" t="n">
-        <v>-245.4184</v>
+        <v>-253.3965</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0104</v>
+        <v>0.0102</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1455</v>
+        <v>0.1425</v>
       </c>
       <c r="J28" t="n">
-        <v>0.0111</v>
+        <v>0.0009</v>
       </c>
       <c r="K28" t="n">
-        <v>0.9163</v>
+        <v>1.0421</v>
       </c>
       <c r="L28" t="s">
         <v>98</v>
@@ -5332,37 +5358,37 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="B29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E29" t="n">
-        <v>-216.6607</v>
+        <v>-258.2594</v>
       </c>
       <c r="F29" t="n">
-        <v>-206.8583</v>
+        <v>-249.3898</v>
       </c>
       <c r="G29" t="n">
-        <v>-217.7542</v>
+        <v>-257.095</v>
       </c>
       <c r="H29" t="n">
-        <v>0.0111</v>
+        <v>0.0081</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1286</v>
+        <v>0.1196</v>
       </c>
       <c r="J29" t="n">
-        <v>0.4058</v>
+        <v>0.0275</v>
       </c>
       <c r="K29" t="n">
-        <v>0.9994</v>
+        <v>1.0533</v>
       </c>
       <c r="L29" t="s">
         <v>98</v>
@@ -5370,10 +5396,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="B30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
@@ -5382,25 +5408,25 @@
         <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>-247.795</v>
+        <v>-214.6785</v>
       </c>
       <c r="F30" t="n">
-        <v>-242.0518</v>
+        <v>-207.6568</v>
       </c>
       <c r="G30" t="n">
-        <v>-246.4102</v>
+        <v>-213.1605</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0103</v>
+        <v>0.0152</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1433</v>
+        <v>0.1594</v>
       </c>
       <c r="J30" t="n">
-        <v>0.0033</v>
+        <v>0.9226</v>
       </c>
       <c r="K30" t="n">
-        <v>1.0385</v>
+        <v>1.1449</v>
       </c>
       <c r="L30" t="s">
         <v>98</v>
@@ -5408,7 +5434,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B31" t="n">
         <v>4</v>
@@ -5420,25 +5446,25 @@
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>-247.3271</v>
+        <v>-253.9111</v>
       </c>
       <c r="F31" t="n">
-        <v>-239.5163</v>
+        <v>-245.8851</v>
       </c>
       <c r="G31" t="n">
-        <v>-246.0538</v>
+        <v>-252.4896</v>
       </c>
       <c r="H31" t="n">
         <v>0.0092</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1212</v>
+        <v>0.1228</v>
       </c>
       <c r="J31" t="n">
-        <v>0.0259</v>
+        <v>0.0073</v>
       </c>
       <c r="K31" t="n">
-        <v>1.1212</v>
+        <v>1.1731</v>
       </c>
       <c r="L31" t="s">
         <v>98</v>
@@ -5446,37 +5472,37 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="B32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" t="n">
         <v>3</v>
       </c>
-      <c r="C32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" t="n">
-        <v>2</v>
-      </c>
       <c r="E32" t="n">
-        <v>-249.884</v>
+        <v>-253.7174</v>
       </c>
       <c r="F32" t="n">
-        <v>-241.283</v>
+        <v>-246.8638</v>
       </c>
       <c r="G32" t="n">
-        <v>-248.9101</v>
+        <v>-252.3118</v>
       </c>
       <c r="H32" t="n">
-        <v>0.0089</v>
+        <v>0.0093</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1229</v>
+        <v>0.1267</v>
       </c>
       <c r="J32" t="n">
-        <v>0.0047</v>
+        <v>0.0317</v>
       </c>
       <c r="K32" t="n">
-        <v>1.1747</v>
+        <v>1.2005</v>
       </c>
       <c r="L32" t="s">
         <v>98</v>
@@ -5484,37 +5510,37 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="B33" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C33" t="n">
         <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>-246.2702</v>
+        <v>-255.3226</v>
       </c>
       <c r="F33" t="n">
-        <v>-239.5905</v>
+        <v>-247.5118</v>
       </c>
       <c r="G33" t="n">
-        <v>-244.9816</v>
+        <v>-254.0493</v>
       </c>
       <c r="H33" t="n">
-        <v>0.0094</v>
+        <v>0.0088</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1281</v>
+        <v>0.1221</v>
       </c>
       <c r="J33" t="n">
-        <v>0.042</v>
+        <v>0.0327</v>
       </c>
       <c r="K33" t="n">
-        <v>1.2056</v>
+        <v>1.2259</v>
       </c>
       <c r="L33" t="s">
         <v>98</v>
@@ -5522,7 +5548,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="B34" t="n">
         <v>1</v>
@@ -5531,28 +5557,28 @@
         <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>-246.0297</v>
+        <v>-251.8911</v>
       </c>
       <c r="F34" t="n">
-        <v>-239.1761</v>
+        <v>-243.8651</v>
       </c>
       <c r="G34" t="n">
-        <v>-244.624</v>
+        <v>-250.4695</v>
       </c>
       <c r="H34" t="n">
-        <v>0.0102</v>
+        <v>0.0094</v>
       </c>
       <c r="I34" t="n">
-        <v>0.141</v>
+        <v>0.1286</v>
       </c>
       <c r="J34" t="n">
-        <v>0.0043</v>
+        <v>0.0315</v>
       </c>
       <c r="K34" t="n">
-        <v>1.2381</v>
+        <v>1.2914</v>
       </c>
       <c r="L34" t="s">
         <v>98</v>
@@ -5560,37 +5586,37 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B35" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C35" t="n">
         <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>-244.4546</v>
+        <v>-253.5344</v>
       </c>
       <c r="F35" t="n">
-        <v>-236.6437</v>
+        <v>-244.6648</v>
       </c>
       <c r="G35" t="n">
-        <v>-243.1812</v>
+        <v>-252.37</v>
       </c>
       <c r="H35" t="n">
-        <v>0.0095</v>
+        <v>0.0088</v>
       </c>
       <c r="I35" t="n">
-        <v>0.1296</v>
+        <v>0.1228</v>
       </c>
       <c r="J35" t="n">
-        <v>0.0443</v>
+        <v>0.0249</v>
       </c>
       <c r="K35" t="n">
-        <v>1.2957</v>
+        <v>1.3042</v>
       </c>
       <c r="L35" t="s">
         <v>98</v>
@@ -5598,37 +5624,37 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>56</v>
+        <v>87</v>
       </c>
       <c r="B36" t="n">
         <v>4</v>
       </c>
       <c r="C36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>-245.7251</v>
+        <v>-251.3725</v>
       </c>
       <c r="F36" t="n">
-        <v>-237.4029</v>
+        <v>-241.8348</v>
       </c>
       <c r="G36" t="n">
-        <v>-244.9505</v>
+        <v>-250.6407</v>
       </c>
       <c r="H36" t="n">
-        <v>0.0088</v>
+        <v>0.0085</v>
       </c>
       <c r="I36" t="n">
-        <v>0.1135</v>
+        <v>0.1084</v>
       </c>
       <c r="J36" t="n">
-        <v>0.0493</v>
+        <v>0.0432</v>
       </c>
       <c r="K36" t="n">
-        <v>1.3859</v>
+        <v>1.4093</v>
       </c>
       <c r="L36" t="s">
         <v>98</v>
@@ -5636,37 +5662,37 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B37" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" t="n">
         <v>2</v>
       </c>
-      <c r="C37" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" t="n">
-        <v>3</v>
-      </c>
       <c r="E37" t="n">
-        <v>-243.5255</v>
+        <v>-248.2993</v>
       </c>
       <c r="F37" t="n">
-        <v>-234.9245</v>
+        <v>-241.2776</v>
       </c>
       <c r="G37" t="n">
-        <v>-242.5516</v>
+        <v>-246.7813</v>
       </c>
       <c r="H37" t="n">
-        <v>0.0091</v>
+        <v>0.0102</v>
       </c>
       <c r="I37" t="n">
-        <v>0.1253</v>
+        <v>0.1436</v>
       </c>
       <c r="J37" t="n">
-        <v>0.0396</v>
+        <v>0.002</v>
       </c>
       <c r="K37" t="n">
-        <v>1.4149</v>
+        <v>1.4216</v>
       </c>
       <c r="L37" t="s">
         <v>98</v>
@@ -5674,37 +5700,37 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="B38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D38" t="n">
         <v>3</v>
       </c>
       <c r="E38" t="n">
-        <v>-244.7469</v>
+        <v>-250.8403</v>
       </c>
       <c r="F38" t="n">
-        <v>-236.4248</v>
+        <v>-241.9708</v>
       </c>
       <c r="G38" t="n">
-        <v>-243.9724</v>
+        <v>-249.676</v>
       </c>
       <c r="H38" t="n">
-        <v>0.0089</v>
+        <v>0.009</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1178</v>
+        <v>0.1252</v>
       </c>
       <c r="J38" t="n">
-        <v>0.0279</v>
+        <v>0.0323</v>
       </c>
       <c r="K38" t="n">
-        <v>1.463</v>
+        <v>1.4289</v>
       </c>
       <c r="L38" t="s">
         <v>98</v>
@@ -5712,37 +5738,37 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>91</v>
+        <v>65</v>
       </c>
       <c r="B39" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D39" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E39" t="n">
-        <v>-241.5315</v>
+        <v>-251.7916</v>
       </c>
       <c r="F39" t="n">
-        <v>-232.9305</v>
+        <v>-243.1906</v>
       </c>
       <c r="G39" t="n">
-        <v>-240.5576</v>
+        <v>-250.8177</v>
       </c>
       <c r="H39" t="n">
-        <v>0.0095</v>
+        <v>0.0089</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1296</v>
+        <v>0.1183</v>
       </c>
       <c r="J39" t="n">
-        <v>0.025</v>
+        <v>0.0093</v>
       </c>
       <c r="K39" t="n">
-        <v>1.5502</v>
+        <v>1.4913</v>
       </c>
       <c r="L39" t="s">
         <v>98</v>
@@ -5750,37 +5776,37 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C40" t="n">
         <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E40" t="n">
-        <v>-238.5421</v>
+        <v>-248.9974</v>
       </c>
       <c r="F40" t="n">
-        <v>-230.7313</v>
+        <v>-240.1278</v>
       </c>
       <c r="G40" t="n">
-        <v>-237.2688</v>
+        <v>-247.833</v>
       </c>
       <c r="H40" t="n">
-        <v>0.0101</v>
+        <v>0.0094</v>
       </c>
       <c r="I40" t="n">
-        <v>0.1401</v>
+        <v>0.1287</v>
       </c>
       <c r="J40" t="n">
-        <v>0.0228</v>
+        <v>0.0176</v>
       </c>
       <c r="K40" t="n">
-        <v>1.6224</v>
+        <v>1.5437</v>
       </c>
       <c r="L40" t="s">
         <v>98</v>
@@ -5788,7 +5814,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B41" t="n">
         <v>2</v>
@@ -5800,25 +5826,25 @@
         <v>4</v>
       </c>
       <c r="E41" t="n">
-        <v>-240.6995</v>
+        <v>-247.9432</v>
       </c>
       <c r="F41" t="n">
-        <v>-231.4909</v>
+        <v>-238.4054</v>
       </c>
       <c r="G41" t="n">
-        <v>-240.2076</v>
+        <v>-247.2114</v>
       </c>
       <c r="H41" t="n">
-        <v>0.009</v>
+        <v>0.0089</v>
       </c>
       <c r="I41" t="n">
-        <v>0.1225</v>
+        <v>0.1228</v>
       </c>
       <c r="J41" t="n">
-        <v>0.0326</v>
+        <v>0.0219</v>
       </c>
       <c r="K41" t="n">
-        <v>1.6393</v>
+        <v>1.6544</v>
       </c>
       <c r="L41" t="s">
         <v>98</v>
@@ -5826,7 +5852,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B42" t="n">
         <v>0</v>
@@ -5838,25 +5864,25 @@
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>-230.621</v>
+        <v>-234.8884</v>
       </c>
       <c r="F42" t="n">
-        <v>-229.0373</v>
+        <v>-233.2773</v>
       </c>
       <c r="G42" t="n">
-        <v>-230.1156</v>
+        <v>-234.3669</v>
       </c>
       <c r="H42" t="n">
-        <v>0.0131</v>
+        <v>0.0133</v>
       </c>
       <c r="I42" t="n">
-        <v>0.1805</v>
+        <v>0.1863</v>
       </c>
       <c r="J42" t="n">
-        <v>0.0161</v>
+        <v>0.019</v>
       </c>
       <c r="K42" t="n">
-        <v>1.7731</v>
+        <v>1.9121</v>
       </c>
       <c r="L42" t="s">
         <v>98</v>
@@ -5864,37 +5890,37 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="B43" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>-239.9528</v>
+        <v>-234.7828</v>
       </c>
       <c r="F43" t="n">
-        <v>-230.3372</v>
+        <v>-227.7611</v>
       </c>
       <c r="G43" t="n">
-        <v>-240.1434</v>
+        <v>-233.2649</v>
       </c>
       <c r="H43" t="n">
-        <v>0.0087</v>
+        <v>0.012</v>
       </c>
       <c r="I43" t="n">
-        <v>0.1228</v>
+        <v>0.1506</v>
       </c>
       <c r="J43" t="n">
-        <v>0.0068</v>
+        <v>0.001</v>
       </c>
       <c r="K43" t="n">
-        <v>1.7847</v>
+        <v>2.0987</v>
       </c>
       <c r="L43" t="s">
         <v>98</v>
@@ -5902,37 +5928,37 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="B44" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C44" t="n">
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E44" t="n">
-        <v>-226.9733</v>
+        <v>-241.7805</v>
       </c>
       <c r="F44" t="n">
-        <v>-222.4812</v>
+        <v>-231.5005</v>
       </c>
       <c r="G44" t="n">
-        <v>-225.7499</v>
+        <v>-242.508</v>
       </c>
       <c r="H44" t="n">
-        <v>0.0132</v>
+        <v>0.0091</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1837</v>
+        <v>0.1257</v>
       </c>
       <c r="J44" t="n">
-        <v>0.0032</v>
+        <v>0.002</v>
       </c>
       <c r="K44" t="n">
-        <v>2.1198</v>
+        <v>2.1815</v>
       </c>
       <c r="L44" t="s">
         <v>98</v>
@@ -5940,37 +5966,37 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C45" t="n">
         <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>-191.5788</v>
+        <v>-231.1246</v>
       </c>
       <c r="F45" t="n">
-        <v>-184.7252</v>
+        <v>-226.5431</v>
       </c>
       <c r="G45" t="n">
-        <v>-190.1731</v>
+        <v>-229.8454</v>
       </c>
       <c r="H45" t="n">
-        <v>0.0187</v>
+        <v>0.0134</v>
       </c>
       <c r="I45" t="n">
-        <v>0.173</v>
+        <v>0.1894</v>
       </c>
       <c r="J45" t="n">
-        <v>0.9923</v>
+        <v>0.0038</v>
       </c>
       <c r="K45" t="n">
-        <v>2.1875</v>
+        <v>2.2585</v>
       </c>
       <c r="L45" t="s">
         <v>98</v>
@@ -5978,7 +6004,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B46" t="n">
         <v>0</v>
@@ -5990,25 +6016,25 @@
         <v>4</v>
       </c>
       <c r="E46" t="n">
-        <v>-189.2921</v>
+        <v>-194.1586</v>
       </c>
       <c r="F46" t="n">
-        <v>-181.4813</v>
+        <v>-186.1326</v>
       </c>
       <c r="G46" t="n">
-        <v>-188.0188</v>
+        <v>-192.7371</v>
       </c>
       <c r="H46" t="n">
-        <v>0.0176</v>
+        <v>0.0181</v>
       </c>
       <c r="I46" t="n">
-        <v>0.2984</v>
+        <v>0.31</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>5.0265</v>
+        <v>5.1357</v>
       </c>
       <c r="L46" t="s">
         <v>98</v>
@@ -6028,25 +6054,25 @@
         <v>3</v>
       </c>
       <c r="E47" t="n">
-        <v>-174.1971</v>
+        <v>-178.2085</v>
       </c>
       <c r="F47" t="n">
-        <v>-167.3435</v>
+        <v>-171.1868</v>
       </c>
       <c r="G47" t="n">
-        <v>-172.7914</v>
+        <v>-176.6906</v>
       </c>
       <c r="H47" t="n">
-        <v>0.0219</v>
+        <v>0.0221</v>
       </c>
       <c r="I47" t="n">
-        <v>0.3933</v>
+        <v>0.3995</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>6.4109</v>
+        <v>6.4359</v>
       </c>
       <c r="L47" t="s">
         <v>98</v>
@@ -6054,7 +6080,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B48" t="n">
         <v>0</v>
@@ -6066,25 +6092,25 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>-136.7152</v>
+        <v>-138.1675</v>
       </c>
       <c r="F48" t="n">
-        <v>-130.972</v>
+        <v>-132.2979</v>
       </c>
       <c r="G48" t="n">
-        <v>-135.3304</v>
+        <v>-136.7009</v>
       </c>
       <c r="H48" t="n">
-        <v>0.0376</v>
+        <v>0.0386</v>
       </c>
       <c r="I48" t="n">
-        <v>0.6811</v>
+        <v>0.709</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>10.9336</v>
+        <v>11.1104</v>
       </c>
       <c r="L48" t="s">
         <v>98</v>
@@ -6092,7 +6118,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B49" t="n">
         <v>0</v>
@@ -6104,25 +6130,25 @@
         <v>1</v>
       </c>
       <c r="E49" t="n">
-        <v>-101.3452</v>
+        <v>-101.8041</v>
       </c>
       <c r="F49" t="n">
-        <v>-96.8531</v>
+        <v>-97.2227</v>
       </c>
       <c r="G49" t="n">
-        <v>-100.1219</v>
+        <v>-100.5249</v>
       </c>
       <c r="H49" t="n">
-        <v>0.0619</v>
+        <v>0.0636</v>
       </c>
       <c r="I49" t="n">
-        <v>1.1508</v>
+        <v>1.1844</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>17.4278</v>
+        <v>17.5297</v>
       </c>
       <c r="L49" t="s">
         <v>98</v>
@@ -6158,7 +6184,7 @@
         <v>48</v>
       </c>
       <c r="C2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3">
